--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_273_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_273_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
         <v>15</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1531,10 +1531,10 @@
         <v>18</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
         <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2321,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>4</v>
@@ -2511,16 +2511,16 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
@@ -2707,7 +2707,7 @@
         <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" t="n">
         <v>2</v>
@@ -3827,16 +3827,16 @@
         <v>138</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>18</v>
@@ -4292,7 +4292,7 @@
         <v>25</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4488,10 +4488,10 @@
         <v>7</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4684,7 +4684,7 @@
         <v>17</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
         <v>2</v>
@@ -5272,10 +5272,10 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5468,16 +5468,16 @@
         <v>25</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
         <v>1</v>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
@@ -5860,7 +5860,7 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -6062,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X44" t="n">
         <v>3</v>
@@ -6252,16 +6252,16 @@
         <v>24</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
         <v>7</v>
@@ -6588,16 +6588,16 @@
         <v>125</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="U47" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="V47" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X47" t="n">
         <v>19</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_273_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_273_EL.xlsx
@@ -674,10 +674,10 @@
         <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="P2" t="n">
         <v>13</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
         <v>17</v>
@@ -851,20 +851,20 @@
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>73.08</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -2327,10 +2327,10 @@
         <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>2</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3503,14 +3503,14 @@
         <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="Y30" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4500,58 +4500,58 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AA36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL36" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5480,14 +5480,14 @@
         <v>2</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
@@ -5524,14 +5524,14 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5709,25 +5709,25 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -6068,14 +6068,14 @@
         <v>2</v>
       </c>
       <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
         <v>3</v>
       </c>
-      <c r="Y44" t="n">
-        <v>5</v>
-      </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6264,10 +6264,10 @@
         <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y45" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6600,14 +6600,14 @@
         <v>6</v>
       </c>
       <c r="X47" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="Y47" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="AA47" t="n">
@@ -6633,25 +6633,25 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AK47" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
